--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\imys java workplace\java workplace\automationtesting\GroceryApplication\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B03E5E-670A-4169-9629-AC38A668AD13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACDB4C1C-FA29-406A-B8C0-1CA60FE3D2C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="1500" windowWidth="28620" windowHeight="13020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="180" yWindow="1500" windowWidth="28620" windowHeight="13020" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="loginpage" sheetId="1" r:id="rId1"/>
     <sheet name="managenews" sheetId="2" r:id="rId2"/>
     <sheet name="adminuser" sheetId="3" r:id="rId3"/>
+    <sheet name="managecategory" sheetId="4" r:id="rId4"/>
+    <sheet name="managecontact" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
   <si>
     <t>Username</t>
   </si>
@@ -63,6 +65,24 @@
   </si>
   <si>
     <t>adminuser123</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>fruit</t>
+  </si>
+  <si>
+    <t>vegetable</t>
+  </si>
+  <si>
+    <t>10AM-2PM</t>
+  </si>
+  <si>
+    <t>delivery time</t>
+  </si>
+  <si>
+    <t>deliverycharge</t>
   </si>
 </sst>
 </file>
@@ -486,4 +506,59 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A0E605E-3420-4FD1-8046-0083A531AB2E}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EABFC47-2D68-4676-8C9D-8ACC4936C4BD}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.5703125" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>